--- a/office/02-测试用例/存储管理/测试用例.xlsx
+++ b/office/02-测试用例/存储管理/测试用例.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>卷格式化-存在可中断I/O时中断服务后执行格式化</t>
+          <t>卷格式化-可中断传输在格式化时被中断</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -3396,41 +3396,41 @@
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. 已使用管理员账号登录TOS，存储管理-卷页面可正常打开；
-2. 卷正在执行可被中断的文件操作（如文件上传）；
-3. 卷无重要数据。</t>
+2. 已准备无重要数据的Volume3，并建立可写入目录/Volume3/642671；
+3. 已准备1个可被中断的外部文件传输任务。</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. 进入存储管理-卷页面；
-2. 启动一个可中断的文件上传；
+2. 从外部客户端通过SSH向/Volume3/642671持续写入大文件；
 3. 选择目标卷，点击格式化并确认；
-4. 观察系统对I/O的处理；
-5. 等待任务完成。</t>
+4. 观察外部传输状态和格式化任务状态；
+5. 等待格式化任务结束。</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. 卷：Volume1。
-2. 文件操作：上传大文件，属可中断服务。
-3. 操作：格式化。</t>
+          <t>1. 卷：Volume3；目标目录：/Volume3/642671。
+2. 可中断传输：外部SSH持续写入大文件，写入速率8 MiB/s。
+3. 触发条件：文件写入约1.7 GiB时发起格式化。</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1. 系统检测到卷存在文件操作，格式化进入处理流程；
-2. 可中断的上传任务被系统中断，该文件不再占用卷；
-3. I/O中断后格式化自动执行成功，页面最终显示完成。</t>
+          <t>1. 格式化启动后能够中断外部SSH传输，客户端出现管道结束或传输失败，测试文件解除占用；
+2. Volume3卸载成功，页面不长期停留在格式化中，任务继续进入格式化阶段；
+3. 格式化完成后页面显示成功，后台文件系统与所选一致，无残留测试文件。</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>可中断/不可中断的判定以技术方案为准</t>
+          <t>2026-09-16实测：17:13:44开始写入，17:17:27传输中断，17:17:28卷卸载，17:17:29格式化为BTRFS，17:17:35任务成功。</t>
         </is>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>卷格式化-存在不可中断I/O时等待占用解除后立即格式化</t>
+          <t>卷格式化-不可中断传输持续占用时等待完成后格式化</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3459,42 +3459,42 @@
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. 已使用管理员账号登录TOS，存储管理-卷页面可正常打开；
-2. 卷正在执行不可中断的文件操作（如正在进行的复制）；
-3. 卷无重要数据。</t>
+2. 已准备无重要数据的Volume3，并建立可写入目录/Volume3/642671；
+3. 已启动1个用于模拟不可中断占用的持续写入进程。</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. 进入存储管理-卷页面；
-2. 启动一个不可中断的文件复制；
+2. 启动本地持续写入进程，向/Volume3/642671写入4 GiB大文件；
 3. 选择目标卷，点击格式化并确认；
-4. 观察任务状态；
-5. 等待复制任务完成；
-6. 观察格式化是否自动执行。</t>
+4. 观察前端任务状态、卷卸载状态和写入进程；
+5. 等待传输自然完成；
+6. 观察格式化是否自动继续执行。</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. 卷：Volume1。
-2. 文件操作：不可中断的复制任务。
-3. 触发条件：复制完成后立即执行格式化。</t>
+          <t>1. 卷：Volume3；目标目录：/Volume3/642671。
+2. 不可中断传输：本地进程持续写入4 GiB大文件，写入速率4 MiB/s。
+3. 触发条件：写入过程中发起格式化，不手动停止写入进程。</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1. 系统检测到卷存在不可中断文件操作，格式化不立即执行，进入等待状态；
-2. 该复制任务正常完成，不被强制中断；
-3. 复制完成、占用解除后系统立即自动执行格式化，无需用户再次操作。</t>
+          <t>1. 前端保持格式化等待状态，不因固定超时而失败，也不强制中断持续写入；
+2. 写入期间卸载请求返回占用中，写入进程继续运行，测试文件大小持续增长；
+3. 写入完成并释放占用后卷自动卸载，格式化继续执行成功，无需用户再次操作。</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>涉及格式化会清空数据，执行前确认卷无重要数据</t>
+          <t>2026-09-16实测：格式化期间后台每约5秒重试卸载并返回target is busy；17:11:32写入完成，17:11:37卸载成功，17:11:45格式化成功；fuser -km /Volume3未识别子目录占用，扫描范围需研发确认。</t>
         </is>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>USB格式化-存在可中断I/O时中断后格式化</t>
+          <t>USB格式化-可中断传输在格式化时被中断</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4714,31 +4714,31 @@
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. 已使用管理员账号登录TOS，存储管理-USB设备页面可正常打开；
-2. USB设备正在执行可被中断的文件操作；
-3. USB设备无重要数据。</t>
+2. 已准备无重要数据的USB1，并建立可写入测试目录；
+3. 已准备1个可被中断的外部文件传输任务。</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. 进入存储管理-USB设备页面；
-2. 启动一个可中断的文件上传；
+2. 从外部客户端向USB共享测试目录持续写入大文件；
 3. 选择目标USB设备，点击格式化并确认；
-4. 观察系统对I/O的处理；
-5. 等待任务完成。</t>
+4. 观察外部传输状态和格式化任务状态；
+5. 等待格式化任务结束。</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. USB设备：USB1。
-2. 文件操作：上传大文件，属可中断服务。
-3. 操作：格式化。</t>
+          <t>1. USB设备：USB1；目标目录：USB共享测试目录。
+2. 可中断传输：外部客户端持续写入大文件，写入速率8 MiB/s。
+3. 触发条件：文件写入约1.7 GiB时发起格式化。</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1. 系统检测到USB存在文件操作，格式化进入处理流程；
-2. 可中断的上传任务被系统中断，该文件不再占用USB；
-3. I/O中断后格式化自动执行成功，页面最终显示完成。</t>
+          <t>1. 格式化启动后能够中断外部传输，客户端出现传输中断，测试文件解除占用；
+2. USB设备卸载成功，页面不长期停留在格式化中，任务继续进入格式化阶段；
+3. 格式化完成后页面显示成功，后台文件系统与所选一致，无残留测试文件。</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>可中断/不可中断的判定以技术方案为准</t>
+          <t>构造方法与卷用例STO-FMT-004一致；USB实机尚未执行，当前仅更新用例内容。</t>
         </is>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>USB格式化-存在不可中断I/O时等待解除后格式化</t>
+          <t>USB格式化-不可中断传输持续占用时等待完成后格式化</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -4777,32 +4777,32 @@
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. 已使用管理员账号登录TOS，存储管理-USB设备页面可正常打开；
-2. USB设备正在执行不可中断的文件操作；
-3. USB设备无重要数据。</t>
+2. 已准备无重要数据的USB1，并建立可写入测试目录；
+3. 已启动1个用于模拟不可中断占用的持续写入进程。</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. 进入存储管理-USB设备页面；
-2. 启动一个不可中断的文件复制；
+2. 启动本地持续写入进程，向USB测试目录写入4 GiB大文件；
 3. 选择目标USB设备，点击格式化并确认；
-4. 观察任务状态；
-5. 等待复制完成；
-6. 观察格式化是否自动执行。</t>
+4. 观察前端任务状态、USB卸载状态和写入进程；
+5. 等待传输自然完成；
+6. 观察格式化是否自动继续执行。</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. USB设备：USB1。
-2. 文件操作：不可中断的复制任务。
-3. 触发条件：复制完成后立即执行格式化。</t>
+          <t>1. USB设备：USB1；目标目录：USB共享测试目录。
+2. 不可中断传输：本地进程持续写入4 GiB大文件，写入速率4 MiB/s。
+3. 触发条件：写入过程中发起格式化，不手动停止写入进程。</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1. 格式化不立即执行，进入等待状态；
-2. 该复制任务正常完成，不被强制中断；
-3. 复制完成、占用解除后系统立即自动执行格式化，无需用户再次操作。</t>
+          <t>1. 前端保持格式化等待状态，不因固定超时而失败，也不强制中断持续写入；
+2. 写入期间USB卸载请求返回占用中，写入进程继续运行，测试文件大小持续增长；
+3. 写入完成并释放占用后USB自动卸载，格式化继续执行成功，无需用户再次操作。</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>涉及格式化会清空USB数据，执行前确认无重要数据</t>
+          <t>构造方法与卷用例STO-FMT-005一致；USB实机尚未执行，当前仅更新用例内容。</t>
         </is>
       </c>
       <c r="K71" s="2" t="n"/>
@@ -11656,8 +11656,3591 @@
       </c>
       <c r="K180" s="2" t="n"/>
     </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-013</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-存在创建中存储池时禁止再次创建</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备可用于新建两个存储池的空闲磁盘。</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 发起创建存储池Pool-A；
+3. 在Pool-A显示创建中时查看并尝试点击创建按钮；
+4. 将鼠标悬停在创建按钮上。</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：创建中；
+2. 检查对象：创建按钮和悬停提示。</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-A处于创建中时创建按钮置灰，点击后不进入创建流程且没有新增创建任务；
+2. 悬停显示“系统正在处理其他存储池的创建或删除操作，请稍后再试”。</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Pool-A为示例名称，执行时可根据实际测试环境替换</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-014</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-存在删除中存储池时禁止创建</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已存在可删除的存储池及可用于新建存储池的空闲磁盘。</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 对现有存储池执行删除；
+3. 在存储池显示删除中时查看并尝试点击创建按钮；
+4. 将鼠标悬停在创建按钮上。</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：删除中；
+2. 检查对象：创建按钮和悬停提示。</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>1. 存在删除中存储池时创建按钮置灰，点击后不进入创建流程；
+2. 悬停显示“系统正在处理其他存储池的创建或删除操作，请稍后再试”。</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>删除测试会清除目标存储池数据，执行前确认无重要数据</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-015</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-可用池挂载中时禁止创建</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备一个可挂载的可用池及可用于新建存储池的空闲磁盘。</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 对可用池执行挂载；
+3. 在可用池显示挂载中时查看并尝试点击创建按钮；
+4. 将鼠标悬停在创建按钮上。</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：可用池挂载中；
+2. 检查对象：创建按钮和悬停提示。</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>1. 可用池挂载中时创建按钮置灰，点击后不进入创建流程；
+2. 悬停仍显示既定文案“系统正在处理其他存储池的创建或删除操作，请稍后再试”。</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>挂载中的提示语按需求保持不变</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-016</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-损坏池挂载中时禁止创建</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备一个可发起挂载的损坏池及可用于新建存储池的空闲磁盘。</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 对损坏池执行挂载；
+3. 在损坏池显示挂载中时查看并尝试点击创建按钮；
+4. 将鼠标悬停在创建按钮上。</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：损坏池挂载中；
+2. 检查对象：创建按钮和悬停提示。</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>1. 损坏池挂载中时创建按钮置灰，点击后不进入创建流程；
+2. 悬停仍显示既定文案“系统正在处理其他存储池的创建或删除操作，请稍后再试”。</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>挂载中的提示语按需求保持不变</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-017</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-存储池同步中时允许创建</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于同步中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看同步中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原同步任务。</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：同步中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>1. 同步中存储池持续显示状态和进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原同步任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-018</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-添加磁盘中时允许创建</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于添加磁盘中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看添加磁盘中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原添加磁盘任务。</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：添加磁盘中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>1. 添加磁盘中存储池持续显示状态和进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原添加磁盘任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-019</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-阵列修复中时允许创建</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于阵列修复中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看阵列修复中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原阵列修复任务。</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：阵列修复中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>1. 页面显示“阵列修复中”及对应进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原阵列修复任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>该状态与热备盘自动补位产生的“修复中”不同</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-020</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-热备盘补位修复中时允许创建</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 热备盘已自动补入降阶冗余池，存储池处于修复中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看热备盘补位后的存储池状态和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原修复任务。</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：修复中，来源为热备盘自动补位；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>1. 页面准确显示“修复中”而不是“阵列修复中”，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原热备盘修复任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>重点区分修复中的触发来源和页面文案</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-021</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-更换磁盘中时允许创建</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于更换磁盘中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看更换磁盘中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原更换磁盘任务。</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：更换磁盘中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>1. 更换磁盘中存储池持续显示状态和进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原更换磁盘任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-022</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-阵列迁移中时允许创建</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于阵列迁移中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看阵列迁移中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原迁移任务。</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：阵列迁移中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列迁移中存储池持续显示状态和进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原迁移任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-023</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-重建中时允许创建</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于重建中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看重建中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原重建任务。</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：重建中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>1. 重建中存储池持续显示状态和进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原重建任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-024</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-数据清理中时允许创建</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于数据清理中且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看数据清理中存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成并继续观察原数据清理任务。</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：数据清理中；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>1. 数据清理中存储池持续显示状态和进度，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原数据清理任务持续执行且进度继续更新。</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-025</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-仅存在正常存储池时允许创建</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 列表仅存在正常存储池且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看正常存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成。</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：正常；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>1. 正常存储池显示在列表中，创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原有正常存储池记录保持不变。</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-026</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-存在降阶存储池时允许创建</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于降阶状态且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看降阶存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成。</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：降阶；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>1. 降阶存储池继续显示且创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原降阶存储池记录和状态保持正确。</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-027</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>创建按钮-存在损坏存储池时允许创建</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已有存储池处于损坏状态但未执行挂载，且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看损坏存储池和创建按钮；
+3. 点击创建按钮，使用1块候选磁盘创建Single存储池Pool-New；
+4. 等待Pool-New创建完成。</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池状态：损坏；
+2. 新建配置：Single，候选磁盘1块。</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>1. 损坏存储池继续显示且创建按钮保持可用；
+2. Pool-New完成创建并显示正常，原损坏池记录保持且没有被错误等同于损坏池挂载中。</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-028</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>状态优先级-同步中与创建中并存时禁止创建</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. Pool-A处于同步中并已准备另一组候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建Pool-B；
+2. 在Pool-A同步中且Pool-B创建中时查看创建按钮；
+3. 等待Pool-B离开创建中。</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态：同步中+创建中；
+2. 状态变化：Pool-B离开创建中并进入同步中或正常。</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态存在创建中时创建按钮置灰，同步中不能覆盖禁止状态；
+2. Pool-B离开创建中且无其他禁止状态后，创建按钮自动恢复可用。</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>Pool-A、Pool-B为示例名称</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-029</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>状态优先级-修复中与删除中并存时禁止创建</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 一个存储池处于修复中，另一个存储池可执行删除。</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>1. 对可删除的存储池执行删除；
+2. 在修复中与删除中同时存在时查看创建按钮；
+3. 等待删除任务结束。</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态：修复中+删除中；
+2. 状态变化：删除任务结束。</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态存在删除中时创建按钮置灰，修复中不能覆盖禁止状态；
+2. 删除任务结束且无其他禁止状态后，创建按钮自动恢复可用，修复任务继续执行。</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>删除测试执行前确认目标池无重要数据</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-030</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>状态优先级-迁移中与可用池挂载中并存时禁止创建</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 一个存储池处于阵列迁移中，并存在可挂载的可用池。</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>1. 对可用池执行挂载；
+2. 在迁移中与可用池挂载中同时存在时查看创建按钮；
+3. 等待挂载任务结束。</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态：阵列迁移中+可用池挂载中；
+2. 状态变化：可用池挂载任务结束。</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态存在挂载中时创建按钮置灰，迁移中不能覆盖禁止状态；
+2. 挂载任务结束且无其他禁止状态后，创建按钮自动恢复可用，迁移任务继续执行。</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-031</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>状态优先级-正常池与损坏池挂载中并存时禁止创建</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 列表存在正常池和可发起挂载的损坏池。</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>1. 对损坏池执行挂载；
+2. 在正常池与损坏池挂载中同时存在时查看创建按钮；
+3. 等待挂载任务结束。</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态：正常+损坏池挂载中；
+2. 状态变化：损坏池挂载任务结束。</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态存在损坏池挂载中时创建按钮置灰，正常状态不能覆盖禁止状态；
+2. 挂载任务结束且无其他禁止状态后，创建按钮按最新状态恢复可用。</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-032</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>状态组合-多个允许状态并存时仍允许创建</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 列表同时存在同步中、修复中、迁移中和降阶等状态，且不存在禁止状态并有候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 核对多个存储池的状态；
+3. 点击创建按钮并进入创建向导；
+4. 取消创建向导。</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>1. 组合状态：同步中+修复中+阵列迁移中+降阶；
+2. 操作：打开创建存储池向导。</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>1. 各存储池状态分别正确显示，创建按钮保持可用；
+2. 创建向导正常打开，已有后台任务均继续执行。</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>组合中的状态可按测试设备能力调整，但不得包含创建中、删除中或挂载中</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-033</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>按钮恢复-最后一个禁止状态结束后自动恢复</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS并停留在存储池页面；
+2. 列表中仅有一个禁止状态任务且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>1. 在禁止任务执行期间观察创建按钮；
+2. 不刷新页面并等待该任务结束；
+3. 点击恢复后的创建按钮；
+4. 取消创建向导。</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>1. 初始状态：创建中、删除中或挂载中之一；
+2. 结束条件：列表中不再存在任何禁止状态。</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>1. 禁止任务执行期间创建按钮保持置灰；
+2. 最后一个禁止状态结束后按钮自动恢复，点击可正常打开创建向导。</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>创建中、删除中和两类挂载中的独立禁止逻辑已由STO-POOL-013至016覆盖</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-034</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>按钮切换-禁止任务开始后立即置灰</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS并停留在存储池页面；
+2. 创建按钮当前可用，列表中存在可执行删除或挂载的存储池。</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>1. 发起删除或挂载任务；
+2. 观察任务状态和创建按钮切换；
+3. 在状态切换期间连续尝试点击创建按钮。</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>1. 状态变化：可用状态→删除中或挂载中；
+2. 操作：状态切换期间连续点击创建按钮。</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>1. 禁止任务开始后创建按钮随状态及时置灰，不依赖刷新页面；
+2. 状态切换期间不会打开新的有效创建流程，也不会生成创建任务。</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>通过当前页面验证，不扩展到接口并发</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-035</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>置灰提示-四类禁止状态保持统一提示语</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 可分别构造创建中、删除中、可用池挂载中和损坏池挂载中。</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>1. 依次构造四类禁止状态；
+2. 每种状态下将鼠标悬停在置灰的创建按钮上；
+3. 记录并比对提示语。</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>1. 禁止状态：创建中、删除中、可用池挂载中、损坏池挂载中；
+2. 目标文案：系统正在处理其他存储池的创建或删除操作，请稍后再试。</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>1. 四种状态下创建按钮均呈一致的不可用样式；
+2. 四种状态的悬停提示均与目标文案一致，不额外增加挂载相关文字。</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>只校验本需求指定提示，不评审文案合理性</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-036</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>默认状态-空存储池列表且有候选磁盘时允许创建</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 当前没有存储池且至少存在一块候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看空列表和创建按钮；
+3. 点击创建按钮；
+4. 取消创建向导。</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池数量：0；
+2. 候选磁盘数量：至少1块。</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>1. 页面正确显示空列表，不出现错误状态；
+2. 创建按钮可用，点击后正常进入创建向导。</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-037</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>置灰原因-无候选磁盘与任务互斥提示相互区分</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 列表不存在禁止状态，但所有磁盘均已被占用。</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 查看创建按钮；
+3. 将鼠标悬停在创建按钮上。</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>1. 禁止状态数量：0；
+2. 候选磁盘数量：0。</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建能力按原有无候选磁盘逻辑限制，不会错误判定为后台任务互斥；
+2. 页面不显示本需求专用于任务互斥的“系统正在处理其他存储池的创建或删除操作”提示。</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>无候选磁盘时的准确提示语沿用现有产品定义</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-038</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-Single创建完成后直接进入正常</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备1块候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用候选磁盘创建Single存储池Pool-Single；
+2. 观察从创建开始到完成的状态；
+3. 创建完成后查看创建按钮。</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：Single，磁盘数量：1块；
+2. 目标状态流转：创建中→正常。</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建过程中存储池显示创建中，完成后Pool-Single直接显示正常；
+2. 不出现同步中状态，离开创建中后创建按钮恢复可用。</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Pool-Single为示例名称</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-039</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-JBOD创建完成后直接进入正常</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备满足JBOD创建条件的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用候选磁盘创建JBOD存储池Pool-JBOD；
+2. 观察从创建开始到完成的状态；
+3. 创建完成后查看创建按钮。</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：JBOD；
+2. 目标状态流转：创建中→正常。</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建过程中存储池显示创建中，完成后Pool-JBOD直接显示正常；
+2. 不出现同步中状态，离开创建中后创建按钮恢复可用。</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>磁盘数量按当前产品JBOD创建条件准备；Pool-JBOD为示例名称</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-040</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-RAID0创建完成后直接进入正常</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备满足RAID0创建条件的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用候选磁盘创建RAID0存储池Pool-RAID0；
+2. 观察从创建开始到完成的状态；
+3. 创建完成后查看创建按钮。</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：RAID0；
+2. 目标状态流转：创建中→正常。</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建过程中存储池显示创建中，完成后Pool-RAID0直接显示正常；
+2. 不出现同步中状态，离开创建中后创建按钮恢复可用。</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>磁盘数量按当前产品RAID0创建条件准备；Pool-RAID0为示例名称</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-041</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-单盘TRAID创建完成后直接进入正常</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备1块支持创建TRAID的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用候选磁盘创建单盘TRAID存储池Pool-TRAID1；
+2. 观察从创建开始到完成的状态；
+3. 创建完成后查看创建按钮。</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：TRAID，磁盘数量：1块；
+2. 目标状态流转：创建中→正常。</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建过程中存储池显示创建中，完成后Pool-TRAID1直接显示正常；
+2. 不出现同步中状态，离开创建中后创建按钮恢复可用。</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>Pool-TRAID1为示例名称</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-042</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-RAID1创建后进入同步并最终正常</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备2块可创建RAID1的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用2块候选磁盘创建RAID1存储池Pool-RAID1；
+2. 观察创建中到同步中的状态切换；
+3. 等待同步完成并查看最终状态和通知。</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：RAID1，磁盘数量：2块；
+2. 目标状态流转：创建中→同步中→正常。</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>1. 存储池离开创建中后进入同步中并显示可持续更新的同步进度；
+2. 同步完成后Pool-RAID1显示正常，状态顺序与目标流转一致，并存在对应的同步完成通知。</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>Pool-RAID1为示例名称</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-043</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>连续创建-冗余池进入同步中后立即允许创建下一存储池</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备创建一个冗余池和另一个新池所需的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建冗余存储池Pool-A；
+2. 保持页面不刷新并观察Pool-A从创建中进入同步中；
+3. Pool-A进入同步中后立即点击创建按钮；
+4. 完成Pool-B创建。</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-A状态变化：创建中→同步中；
+2. 后续操作：在Pool-A同步期间创建Pool-B。</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-A处于创建中时按钮置灰，进入同步中后按钮自动恢复且没有多余延迟要求；
+2. Pool-B可以完成创建，Pool-A同步任务持续执行且记录不丢失。</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>Pool-A、Pool-B为示例名称</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-044</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>重复操作-创建提交阶段连续点击不产生两个创建中任务</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备一组可创建存储池的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入创建存储池向导并填写有效配置；
+2. 在最终确认处快速连续点击确认按钮；
+3. 返回存储池列表并观察创建记录。</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建配置：一组有效候选磁盘和一个有效阵列类型；
+2. 操作次数：最终确认按钮快速连续点击5次。</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建请求进入处理后确认按钮不可重复生效，页面不出现重复提交异常；
+2. 列表最多新增一个目标存储池，任意时刻最多一个存储池显示创建中。</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>点击5次为示例值；仅验证当前页面重复操作，不包含接口或多浏览器并发</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-045</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>连续创建-前两个存储池同步期间创建第三个存储池</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备创建三个存储池所需的候选磁盘，其中前两个为冗余阵列。</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建Pool-A并等待其进入同步中；
+2. 创建Pool-B并等待其进入同步中；
+3. 在Pool-A和Pool-B同时同步时创建Pool-C；
+4. 查看三个存储池的任务状态。</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>1. 并行背景：Pool-A和Pool-B同时同步；
+2. 新建对象：Pool-C。</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>1. 两个同步任务并存时创建按钮可用，Pool-A和Pool-B状态及进度持续更新；
+2. Pool-C能够完成创建，三个存储池记录均保留且互不覆盖。</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Pool-A、Pool-B、Pool-C为示例名称；需要足够的独立候选磁盘</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-046</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>连续创建-冗余与无冗余阵列混合创建状态正确</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备创建冗余阵列、Single和RAID0所需的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>1. 创建冗余Pool-A并等待进入同步中；
+2. 在Pool-A同步期间创建Single Pool-B并等待正常；
+3. 在Pool-A仍同步时创建RAID0 Pool-C并等待正常；
+4. 查看所有存储池状态。</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列组合：多盘冗余阵列+Single+RAID0；
+2. 创建顺序：Pool-A→Pool-B→Pool-C。</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-A显示同步中，Pool-B和Pool-C创建完成后直接显示正常；
+2. 三次创建可按顺序完成，已有池的状态和任务不被后续创建改变。</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>Pool-A、Pool-B、Pool-C为示例名称</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-047</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>任务展示-多个后台任务的名称状态和进度相互独立</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 至少两个不同存储池正在执行可观察进度的后台任务。</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入存储管理-存储池页面；
+2. 连续观察各存储池名称、状态和进度变化；
+3. 等待其中一个任务完成；
+4. 继续观察其他任务。</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>1. 任务对象：至少2个不同名称的存储池；
+2. 观察内容：名称、状态、进度和完成结果。</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>1. 每个存储池的名称、状态和进度一一对应，不出现状态串池或进度串池；
+2. 一个任务完成只更新对应存储池，其他任务保持各自进度并继续执行。</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-048</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>任务组合-同步修复迁移等后台任务并行时允许创建</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 可同时构造同步中、修复中及阵列迁移中等至少三种允许状态，且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>1. 启动并确认各后台任务进入对应状态；
+2. 查看存储池列表和创建按钮；
+3. 创建一个新的存储池；
+4. 观察原有任务和新建存储池。</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>1. 后台任务组合：同步中+修复中+阵列迁移中等至少3种允许状态；
+2. 新建对象：一个使用剩余候选磁盘的存储池。</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>1. 多种允许状态并行时创建按钮可用，各后台任务持续显示和执行；
+2. 新存储池完成创建，原有任务的状态、进度和结果互不受影响。</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>具体组合按测试设备磁盘数量选择并记录，不得包含禁止状态</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-049</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>任务隔离-单个同步任务完成不影响其他后台任务</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 至少两个存储池同时执行后台任务，其中一个即将同步完成。</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录各存储池当前状态和进度；
+2. 等待目标存储池同步完成；
+3. 查看目标池和其他池的状态、进度；
+4. 查看创建按钮。</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>1. 目标事件：一个存储池同步完成；
+2. 对照对象：其他仍在执行后台任务的存储池。</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>1. 目标存储池更新为正常并保留正确记录；
+2. 其他存储池任务不停止、不重置且进度继续更新，创建按钮仍按全局状态正确判断。</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-050</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>数据持久化-页面刷新后后台任务展示保持正确</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 多个存储池正在同步、修复或迁移。</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录刷新前各存储池名称、状态和进度；
+2. 刷新浏览器页面；
+3. 重新进入存储管理-存储池页面；
+4. 对比刷新前后展示。</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>1. 刷新对象：包含多个后台任务的存储池页面；
+2. 对比字段：存储池记录、状态、进度和创建按钮。</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>1. 刷新后所有任务记录仍在，页面没有重复或遗漏存储池；
+2. 状态和进度反映刷新后的真实任务情况，创建按钮判断与当前全局状态一致。</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-051</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>热备盘修复-降阶到修复中再恢复正常的完整流转</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备带热备盘的冗余存储池且池内无重要数据。</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>1. 拔出冗余存储池的一块成员盘；
+2. 观察存储池降阶及热备盘自动补位；
+3. 在修复中打开创建存储池向导后取消；
+4. 等待修复完成并查看最终状态。</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发方式：拔出1块冗余阵列成员盘并由热备盘自动补位；
+2. 目标状态流转：降阶→修复中→正常。</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>1. 热备盘补位后状态显示“修复中”，该状态下创建按钮可用且创建向导可打开；
+2. 修复完成后存储池恢复正常，完整状态流转与目标一致。</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>涉及拔盘操作，必须使用无重要数据的测试存储池</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-052</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>通知-单个存储池同步完成后产生对应通知</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 一个冗余存储池正在同步且通知功能可查看。</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录同步中的存储池名称；
+2. 等待同步完成；
+3. 查看存储池最终状态；
+4. 查看通知记录。</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>1. 事件：目标存储池同步完成；
+2. 校验标识：目标存储池名称。</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>1. 目标存储池同步完成并显示正常；
+2. 存在与同步完成事件对应的通知，通知能够对应目标存储池。</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>不检查通知精确文案、级别、位置、顺序和去重规则</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-053</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>通知-多个存储池同步完成通知与池标识一一对应</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 至少两个名称不同的存储池同时或先后同步，通知功能可查看。</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录每个同步中存储池的名称；
+2. 等待各存储池分别同步完成；
+3. 查看通知记录并与存储池名称对应。</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>1. 同步对象：至少2个名称不同的存储池；
+2. 校验内容：每个池的同步完成事件和通知标识。</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>1. 每个存储池均按自身进度完成同步，不受其他池完成时间影响；
+2. 每个同步完成事件都有对应通知，通知不会匹配到错误的存储池。</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>不检查通知顺序和去重规则</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-054</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>通知-存储池进入降阶后产生对应通知</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 已准备可安全拔出一块成员盘的冗余测试存储池，且通知功能可查看。</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录目标存储池名称和当前状态；
+2. 拔出一块阵列成员盘；
+3. 查看存储池状态；
+4. 查看通知记录。</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>1. 异常操作：拔出目标冗余池的1块成员盘；
+2. 校验标识：目标存储池名称。</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>1. 目标存储池进入降阶状态并继续显示在列表中；
+2. 存在对应的降阶通知，通知能够对应目标存储池。</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>涉及拔盘操作，必须使用无重要数据的测试存储池；不检查通知精确文案等非重点属性</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-055</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>同步异常-拔出一块成员盘后同步继续并最终降阶</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 冗余测试存储池正在同步且池内无重要数据。</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录目标池当前同步进度；
+2. 拔出目标池的一块成员盘；
+3. 持续观察同步状态和进度；
+4. 等待同步结束并查看最终状态和创建按钮。</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>1. 异常操作：同步过程中拔出1块阵列成员盘；
+2. 目标结果：同步继续并在完成后显示降阶；
+3. 通知事件：拔盘降阶和后续同步完成。</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>1. 拔盘后目标池记录不消失，同步任务继续且进度可更新；
+2. 同步完成后目标池显示降阶，创建按钮不因降阶状态单独置灰；
+3. 降阶时存在对应降阶通知，同步结束时存在对应同步完成通知，两项通知均匹配目标池。</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>涉及拔盘操作，必须使用无重要数据的测试存储池</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-056</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>同步异常-拔出全部成员盘后存储池进入损坏</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 冗余测试存储池正在同步且池内无重要数据，另有候选磁盘可创建新池。</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>1. 在同步过程中依次拔出目标池的全部成员盘；
+2. 观察目标存储池状态和列表记录；
+3. 查看创建按钮并打开创建向导；
+4. 取消创建向导。</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>1. 异常操作：拔出目标池的全部成员盘；
+2. 后续操作：使用其他候选磁盘打开创建向导。</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>1. 目标存储池进入损坏状态且记录继续显示，不被错误删除或隐藏；
+2. 损坏状态不会单独阻止创建，创建按钮可用且向导可打开。</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>涉及全部成员盘拔出，必须使用专用无重要数据测试池</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-057</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>任务隔离-一个同步池成员盘异常不影响其他存储池</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. Pool-A和Pool-B同时同步且Pool-A内无重要数据。</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录Pool-A和Pool-B的同步进度；
+2. 拔出Pool-A的一块成员盘；
+3. 持续观察两个存储池的任务；
+4. 等待两个任务分别结束。</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>1. 异常对象：Pool-A，拔出1块成员盘；
+2. 对照对象：同步中的Pool-B。</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-A按异常流程继续同步并最终降阶，不影响其任务记录；
+2. Pool-B同步不中止、不失败、不重置进度并按自身流程完成。</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>Pool-A、Pool-B为示例名称；涉及拔盘操作，必须使用无重要数据的测试存储池</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-058</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>网络恢复-管理端与NAS断网后任务记录保留</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 多个存储池正在执行同步等后台任务。</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录断网前各存储池状态和进度；
+2. 断开管理端与NAS之间的网络连接；
+3. 保持断网一段时间后恢复连接；
+4. 重新进入存储池页面并查看任务。</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>1. 中断类型：仅管理端与NAS之间网络断开；
+2. 中断时长：5分钟。</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>1. 管理端断网不会导致NAS本地任务被取消或生成重复任务；
+2. 网络恢复后原任务记录仍在，页面展示当前真实状态和进度。</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>5分钟为示例值，执行时可根据任务时长调整</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-059</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>网络恢复-NAS网络或网络服务中断后任务记录保留</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 多个存储池正在执行同步等后台任务。</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录中断前各存储池状态和进度；
+2. 中断NAS自身网络连接或停止并恢复相关网络服务；
+3. 保持中断一段时间后恢复NAS网络；
+4. 重新进入存储池页面并查看任务。</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>1. 中断类型：NAS网络连接中断或NAS网络服务中断；
+2. 中断时长：5分钟。</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>1. NAS网络异常期间本地存储任务记录不丢失且不产生重复任务；
+2. 网络恢复后原任务记录仍在，页面展示当前真实状态和进度。</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>网络连接中断与网络服务中断可分两轮执行；5分钟为示例值</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-060</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>断电恢复-创建中异常断电后任务记录保留</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 已准备无重要数据的候选磁盘并可安全执行测试机断电。</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>1. 发起创建一个冗余存储池；
+2. 在存储池显示创建中时切断测试NAS电源；
+3. 重新通电并等待TOS启动；
+4. 登录后查看存储池页面。</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>1. 断电时点：存储池创建中；
+2. 恢复方式：重新通电并登录TOS。</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>1. 异常断电不会导致该存储池的原任务记录无故消失或产生重复记录；
+2. 重启后页面展示该池当前真实状态，可能为重建中等恢复状态。</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>高风险断电测试，仅在专用测试NAS和无重要数据环境执行；不要求恢复到断电前精确进度</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-061</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>断电恢复-刚进入同步中断电后任务记录保留</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 已创建无重要数据的冗余测试存储池。</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>1. 等待目标池从创建中刚进入同步中；
+2. 切断测试NAS电源；
+3. 重新通电并等待TOS启动；
+4. 登录后查看存储池任务记录和状态。</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>1. 断电时点：目标池刚进入同步中；
+2. 校验对象：原存储池任务记录和重启后状态。</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>1. 重启后原存储池和任务记录仍存在，不出现重复或丢失；
+2. 页面显示重建中或其他当前真实状态，创建按钮按该状态及全局状态正确判断。</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>高风险断电测试，仅在专用测试NAS和无重要数据环境执行；不要求恢复到断电前精确进度</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-062</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>断电恢复-同步接近完成时断电后任务记录保留</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS；
+2. 无重要数据的冗余测试存储池正在同步。</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>1. 等待目标池同步接近完成；
+2. 切断测试NAS电源；
+3. 重新通电并等待TOS启动；
+4. 登录后查看存储池任务记录和状态。</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>1. 断电时点：同步进度约90%；
+2. 校验对象：原存储池任务记录和重启后状态。</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>1. 重启后原存储池和任务记录仍存在，不出现重复或丢失；
+2. 页面显示重建中、同步中或其他当前真实状态，不要求从断电前百分比继续。</t>
+        </is>
+      </c>
+      <c r="I230" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>90%为示例时点；高风险断电测试，仅在专用测试NAS和无重要数据环境执行</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-063</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>性能稳定性-逐步增加并行后台任务资源占用不越红线</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>1. 已记录测试NAS型号、CPU、内存和磁盘环境；
+2. 已准备可构造多个存储池后台任务的无重要数据磁盘。</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>1. 启动第一组存储池同步任务并开始持续监控CPU、内存和磁盘I/O；
+2. 在磁盘条件允许时逐步增加同步、修复或迁移任务；
+3. 每增加一个任务记录任务数量和资源峰值；
+4. 持续观察至任务完成或任一资源达到红线。</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>1. 并行任务规模：从1个开始逐步增加至现有磁盘允许的最大规模；
+2. 资源红线：CPU&lt;80%，内存&lt;90%；
+3. 辅助观察项：磁盘I/O使用率和响应延迟。</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>1. 每个规模下任务均可启动和持续执行，并记录可复现的任务组合；
+2. 整个监控期间CPU始终低于80%且内存始终低于90%，任一指标达到或超过红线即判定不通过；
+3. 磁盘I/O和响应延迟有连续记录，可用于定位卡顿或任务停滞。</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>当前不预设并行任务上限；若发现重大问题，记录首次稳定复现的问题规模并交由产品评估上限</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-064</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>性能稳定性-多任务期间页面和存储管理服务保持可用</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>1. 已记录当前测试NAS环境；
+2. 多个存储池正在同步、修复或迁移。</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>1. 多次打开和刷新存储池页面；
+2. 查看各任务状态和进度；
+3. 执行打开创建向导、切换存储管理版块等页面操作；
+4. 持续观察系统和存储管理服务。</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>1. 运行背景：多个存储池后台任务并行；
+2. 观察时长：至少覆盖一个后台任务从运行到完成。</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>1. 页面可访问和操作，任务进度持续更新，不出现长期Loading、明显卡死或页面崩溃；
+2. TOS和存储管理服务不崩溃、不异常重启，NAS不死机。</t>
+        </is>
+      </c>
+      <c r="I232" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>观察时长按实际后台任务耗时记录</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-065</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>性能稳定性-高负载期间创建按钮判断和任务进度准确</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>1. 已记录当前测试NAS环境；
+2. 多个允许状态后台任务并行且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>1. 在多任务运行期间观察创建按钮并创建一个新存储池；
+2. 新池创建中时观察创建按钮和全部任务进度；
+3. 新池离开创建中后再次观察创建按钮；
+4. 持续监控任务状态直到新池进入同步中或正常。</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>1. 初始组合：多个允许状态后台任务并行；
+2. 状态变化：允许状态→增加创建中→创建中结束。</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>1. 高负载下仍可正常发起新建；新池创建中时按钮置灰且各池进度不串池、不停滞；
+2. 新池离开创建中后按钮按最新全局状态恢复，所有状态和进度显示准确。</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>执行期间同时记录CPU、内存和磁盘I/O</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-066</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>权限回归-无创建权限用户不因后台状态放开而获得创建能力</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>1. 已存在无存储池创建权限的普通用户；
+2. 列表中仅存在同步中或正常等允许状态且有候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用无创建权限用户登录TOS；
+2. 进入存储管理-存储池页面；
+3. 查看并尝试使用创建入口。</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>1. 用户权限：无存储池创建权限；
+2. 存储池状态：仅存在允许状态。</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>1. 用户权限保持原有受限状态，不能发起存储池创建；
+2. 允许后台任务期间创建的新规则不会绕过原有权限控制。</t>
+        </is>
+      </c>
+      <c r="I234" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>创建入口隐藏或置灰等具体表现沿用现有权限设计</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-067</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>列表联动-新建存储池加入列表不覆盖已有任务记录</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 列表中已有多个正常或任务中的存储池，且存在候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录创建前所有存储池名称和状态；
+2. 创建一个新存储池；
+3. 新存储池加入列表后核对全部记录；
+4. 刷新页面后再次核对。</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>1. 原有对象：至少2个名称不同的存储池；
+2. 新建对象：一个名称不同的新存储池。</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>1. 新存储池作为独立记录加入列表，原有存储池不被覆盖、隐藏或错误刷新；
+2. 刷新后所有存储池记录、名称和状态保持正确。</t>
+        </is>
+      </c>
+      <c r="I235" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>存储池名称使用符合当前产品命名规则的示例值</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-068</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>数据持久化-切换版块并重新登录后任务展示保持正确</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 多个存储池正在同步、修复或迁移。</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>1. 记录各存储池名称、状态、进度和创建按钮状态；
+2. 切换到存储管理其他版块后返回存储池页面；
+3. 退出当前账号并重新登录TOS；
+4. 再次进入存储池页面并对比展示。</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>1. 页面操作：切换存储管理版块后返回；
+2. 会话操作：退出并重新登录当前管理员账号。</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>1. 返回存储池页面后原任务记录仍在，状态和进度反映当前真实任务情况；
+2. 重新登录后记录不丢失、不重复，创建按钮按当前全局状态正确判断。</t>
+        </is>
+      </c>
+      <c r="I236" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-069</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-RAID5创建后进入同步并最终正常</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备3块可创建RAID5的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用3块候选磁盘创建RAID5存储池Pool-RAID5；
+2. 观察创建中到同步中的状态切换；
+3. 等待同步完成并查看最终状态和通知。</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：RAID5，磁盘数量：3块；
+2. 目标状态流转：创建中→同步中→正常。</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-RAID5离开创建中后进入同步中并显示可持续更新的进度；
+2. 同步完成后显示正常并存在对应的同步完成通知。</t>
+        </is>
+      </c>
+      <c r="I237" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>Pool-RAID5为示例名称</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-070</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-RAID6创建后进入同步并最终正常</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备4块可创建RAID6的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用4块候选磁盘创建RAID6存储池Pool-RAID6；
+2. 观察创建中到同步中的状态切换；
+3. 等待同步完成并查看最终状态和通知。</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：RAID6，磁盘数量：4块；
+2. 目标状态流转：创建中→同步中→正常。</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-RAID6离开创建中后进入同步中并显示可持续更新的进度；
+2. 同步完成后显示正常并存在对应的同步完成通知。</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>Pool-RAID6为示例名称</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-071</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-RAID10创建后进入同步并最终正常</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备4块可创建RAID10的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用4块候选磁盘创建RAID10存储池Pool-RAID10；
+2. 观察创建中到同步中的状态切换；
+3. 等待同步完成并查看最终状态和通知。</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：RAID10，磁盘数量：4块；
+2. 目标状态流转：创建中→同步中→正常。</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-RAID10离开创建中后进入同步中并显示可持续更新的进度；
+2. 同步完成后显示正常并存在对应的同步完成通知。</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>Pool-RAID10为示例名称</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-072</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-多盘TRAID创建后进入同步并最终正常</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备2块可创建多盘TRAID的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用2块候选磁盘创建TRAID存储池Pool-TRAID；
+2. 观察创建中到同步中的状态切换；
+3. 等待同步完成并查看最终状态和通知。</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：TRAID，磁盘数量：2块；
+2. 目标状态流转：创建中→同步中→正常。</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>1. 多盘Pool-TRAID离开创建中后进入同步中并显示可持续更新的进度；
+2. 同步完成后显示正常并存在对应的同步完成通知。</t>
+        </is>
+      </c>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>Pool-TRAID为示例名称；与单盘TRAID直接进入正常的流程区分</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>STO-POOL-073</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>存储管理-存储池</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>状态流转-TRAID+创建后进入同步并最终正常</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>1. 已使用管理员账号登录TOS，存储管理可正常打开；
+2. 已准备4块可创建TRAID+的候选磁盘。</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用4块候选磁盘创建TRAID+存储池Pool-TRAIDPlus；
+2. 观察创建中到同步中的状态切换；
+3. 等待同步完成并查看最终状态和通知。</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>1. 阵列类型：TRAID+，磁盘数量：4块；
+2. 目标状态流转：创建中→同步中→正常。</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>1. Pool-TRAIDPlus离开创建中后进入同步中并显示可持续更新的进度；
+2. 同步完成后显示正常并存在对应的同步完成通知。</t>
+        </is>
+      </c>
+      <c r="I241" s="3" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>Pool-TRAIDPlus为示例名称；若测试机不支持TRAID+则记录为环境阻塞</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="n"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I180">
+  <conditionalFormatting sqref="I2:I241">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"通过"</formula>
     </cfRule>
@@ -11672,7 +15255,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I241" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败,阻塞,未执行"</formula1>
     </dataValidation>
   </dataValidations>
